--- a/data/capstone-designing-a-factorial-experiment.xlsx
+++ b/data/capstone-designing-a-factorial-experiment.xlsx
@@ -4269,7 +4269,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4783,7 +4782,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Line speed, 8 or 12 metres per minute.</t>
+          <t>Line speed, 8 or 12 meters per minute.</t>
         </is>
       </c>
     </row>
